--- a/assets/xlsx/투자자산현황_2026-08-27_2026-08-27.xlsx
+++ b/assets/xlsx/투자자산현황_2026-08-27_2026-08-27.xlsx
@@ -20,7 +20,7 @@
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -33,11 +33,6 @@
       <b val="1"/>
       <color rgb="00111827"/>
       <sz val="13"/>
-    </font>
-    <font>
-      <name val="맑은 고딕"/>
-      <color rgb="009CA3AF"/>
-      <sz val="9"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
@@ -101,21 +96,20 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="10" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -481,7 +475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18.5" customWidth="1" min="1" max="1"/>
@@ -500,121 +494,107 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>※ 예시값 — 표기 금액·요율·상호는 전부 예시이며 실제 거래 기록이 아니다. 수수료율은 미확정이고 할인율 0.11%는 예정값이다.</t>
-        </is>
-      </c>
-    </row>
     <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>자산 구분</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>금액 (원)</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>W금융일수</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>S입금부족율</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Ty수익율</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>비중</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>보관</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>투자실행액</t>
         </is>
       </c>
-      <c r="B4" s="5" t="n">
+      <c r="B4" s="4" t="n">
         <v>1523100000</v>
       </c>
-      <c r="C4" s="6" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="D4" s="7" t="n">
+      <c r="C4" s="5" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D4" s="6" t="n">
         <v>0.0042</v>
       </c>
-      <c r="E4" s="7" t="n">
-        <v>0.0357</v>
-      </c>
-      <c r="F4" s="8" t="n">
+      <c r="E4" s="6" t="n">
+        <v>0.1295</v>
+      </c>
+      <c r="F4" s="7" t="n">
         <v>0.9350000000000001</v>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>㈜페이허그</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>순현금</t>
         </is>
       </c>
-      <c r="B5" s="5" t="n">
+      <c r="B5" s="4" t="n">
         <v>105300000</v>
       </c>
-      <c r="C5" s="4" t="n"/>
-      <c r="D5" s="4" t="n"/>
-      <c r="E5" s="4" t="n"/>
-      <c r="F5" s="8" t="n">
+      <c r="C5" s="3" t="n"/>
+      <c r="D5" s="3" t="n"/>
+      <c r="E5" s="3" t="n"/>
+      <c r="F5" s="7" t="n">
         <v>0.065</v>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>㈜쿠콘</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>합계 (투자자산)</t>
         </is>
       </c>
-      <c r="B6" s="10" t="n">
+      <c r="B6" s="9" t="n">
         <v>1628400000</v>
       </c>
-      <c r="C6" s="9" t="n"/>
-      <c r="D6" s="9" t="n"/>
-      <c r="E6" s="9" t="n"/>
-      <c r="F6" s="11" t="n">
+      <c r="C6" s="8" t="n"/>
+      <c r="D6" s="8" t="n"/>
+      <c r="E6" s="8" t="n"/>
+      <c r="F6" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="G6" s="9" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>※ 합계(투자자산) = 투자실행액 + 순현금. W금융일수·S입금부족율·Ty수익율은 투자실행액에만 산정.</t>
-        </is>
-      </c>
+      <c r="G6" s="8" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/assets/xlsx/투자자산현황_2026-08-27_2026-08-27.xlsx
+++ b/assets/xlsx/투자자산현황_2026-08-27_2026-08-27.xlsx
@@ -474,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18.5" customWidth="1" min="1" max="1"/>
@@ -493,6 +493,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -517,16 +518,6 @@
       <c r="E3" s="2" t="inlineStr">
         <is>
           <t>예상 연환산 수익률</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>비중</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>보관</t>
         </is>
       </c>
     </row>
@@ -548,14 +539,6 @@
       <c r="E4" s="6" t="n">
         <v>0.1321</v>
       </c>
-      <c r="F4" s="7" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>㈜페이허그</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -569,14 +552,6 @@
       <c r="C5" s="3" t="n"/>
       <c r="D5" s="3" t="n"/>
       <c r="E5" s="3" t="n"/>
-      <c r="F5" s="7" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>㈜쿠콘</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" s="8" t="inlineStr">
@@ -590,14 +565,10 @@
       <c r="C6" s="8" t="n"/>
       <c r="D6" s="8" t="n"/>
       <c r="E6" s="8" t="n"/>
-      <c r="F6" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" s="8" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A1:E1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/assets/xlsx/투자자산현황_2026-08-27_2026-08-27.xlsx
+++ b/assets/xlsx/투자자산현황_2026-08-27_2026-08-27.xlsx
@@ -16,9 +16,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="0.0%"/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="5">
     <font>
       <name val="Calibri"/>
@@ -95,7 +93,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -105,10 +103,8 @@
     <xf numFmtId="3" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -482,8 +478,6 @@
     <col width="12.5" customWidth="1" min="3" max="3"/>
     <col width="14.5" customWidth="1" min="4" max="4"/>
     <col width="11.5" customWidth="1" min="5" max="5"/>
-    <col width="11.5" customWidth="1" min="6" max="6"/>
-    <col width="13.5" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -493,7 +487,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -554,17 +547,17 @@
       <c r="E5" s="3" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>합계 (투자자산)</t>
         </is>
       </c>
-      <c r="B6" s="9" t="n">
+      <c r="B6" s="8" t="n">
         <v>100000000</v>
       </c>
-      <c r="C6" s="8" t="n"/>
-      <c r="D6" s="8" t="n"/>
-      <c r="E6" s="8" t="n"/>
+      <c r="C6" s="7" t="n"/>
+      <c r="D6" s="7" t="n"/>
+      <c r="E6" s="7" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
